--- a/02_activities/assignments/Assignment_one_1.xlsx
+++ b/02_activities/assignments/Assignment_one_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NEWPC\shell\sql\02_activities\assignments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A8A58C-E3E5-4EE4-B1EE-4C4DFEF1408B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675D566F-764E-47F3-9F36-C8FED1D0EE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{13621D78-2D0A-4DC5-A788-B79851150635}"/>
   </bookViews>
@@ -184,8 +184,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,10 +625,20 @@
   </cols>
   <sheetData>
     <row r="4" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D4" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="E4" s="6"/>
       <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="7" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="4:9" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -690,6 +700,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
